--- a/artfynd/A 50351-2021 artfynd.xlsx
+++ b/artfynd/A 50351-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50351-2021 artfynd.xlsx
+++ b/artfynd/A 50351-2021 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63189502</v>
+        <v>63200941</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -739,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564222.8042080699</v>
+        <v>564223</v>
       </c>
       <c r="R2" t="n">
-        <v>6256705.219320182</v>
+        <v>6256705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,19 +767,9 @@
           <t>2012-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,12 +804,7 @@
         <v>63202749</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564222.8042080699</v>
+        <v>564223</v>
       </c>
       <c r="R3" t="n">
-        <v>6256705.219320182</v>
+        <v>6256705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,19 +893,9 @@
           <t>2012-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -957,42 +927,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63200941</v>
+        <v>63189502</v>
       </c>
       <c r="B4" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1021,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564222.8042080699</v>
+        <v>564223</v>
       </c>
       <c r="R4" t="n">
-        <v>6256705.219320182</v>
+        <v>6256705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1054,19 +1019,9 @@
           <t>2012-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
